--- a/Campusano_territory_chart.xlsx
+++ b/Campusano_territory_chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yanuriscampusano\Music\data_labs3\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{2DD9A4ED-589A-4606-A0AF-52C8518BA9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CD8D6F-61FC-4FA3-8A9C-CCCF751A6F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="17436" windowHeight="14496" firstSheet="1" activeTab="2" xr2:uid="{3A3ABD6E-29B3-44B9-BCDA-4D764EC285EF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" firstSheet="1" activeTab="2" xr2:uid="{3A3ABD6E-29B3-44B9-BCDA-4D764EC285EF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -19,13 +19,13 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
   <si>
     <t>Year</t>
   </si>
@@ -44,12 +44,15 @@
   <si>
     <t>Sum of Monthly_Revenue</t>
   </si>
+  <si>
+    <t>This chart shows New Jersey territory monthly revenue from 2022 to 2025. You can see a clear upward trend. Revenue started around $63,000 to $84,000 per month in 2022 and grew consistently to over $140,000 per month by late 2024. The territory doubled its monthly revenue over this period which shows strong overall growth. The notable spike in October 2025 hitting $250,830 is unusual but it could be a large bulk purchase or a very successful marketing campaign that they should repeat it.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,6 +191,13 @@
       <b/>
       <u/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -547,11 +557,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -624,7 +636,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[campusano_territory_chart.xlsx]Sheet1!PivotTable2</c:name>
+    <c:name>[Campusano_territory_chart.xlsx]Sheet1!PivotTable2</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1075,53 +1087,51 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[campusano_territory_chart.xlsx]Chart!PivotTable3</c:name>
-    <c:fmtId val="0"/>
+    <c:name>[Campusano_territory_chart.xlsx]Chart!PivotTable3</c:name>
+    <c:fmtId val="19"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="0"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
                   </a:schemeClr>
                 </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
+              <a:rPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
               </a:rPr>
               <a:t>New Jersey Territory — Monthly Revenue 2022-2025</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:endParaRPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.12995490443754501"/>
-          <c:y val="7.990937752499247E-2"/>
-        </c:manualLayout>
-      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1131,17 +1141,23 @@
         <a:effectLst/>
       </c:spPr>
       <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="0"/>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -1156,21 +1172,56 @@
       <c:pivotFmt>
         <c:idx val="0"/>
         <c:spPr>
-          <a:ln w="28575" cap="rnd">
+          <a:ln w="34925" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent6"/>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:round/>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
           <c:spPr>
-            <a:noFill/>
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1185,10 +1236,7 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="tx1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -1200,6 +1248,95 @@
           </c:txPr>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="34925" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -1230,17 +1367,202 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="34925" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent6"/>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
           </c:marker>
+          <c:dPt>
+            <c:idx val="45"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="6"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst>
+                  <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                    <a:srgbClr val="000000">
+                      <a:alpha val="63000"/>
+                    </a:srgbClr>
+                  </a:outerShdw>
+                </a:effectLst>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="34925" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-3D8F-4520-9565-638FD5563021}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="45"/>
+              <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-3D8F-4520-9565-638FD5563021}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
               <c:f>Chart!$A$2:$A$54</c:f>
@@ -1565,7 +1887,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6DFE-4FE9-8A00-F0036E7AD81C}"/>
+              <c16:uniqueId val="{00000000-3D8F-4520-9565-638FD5563021}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1577,17 +1899,84 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="272478047"/>
-        <c:axId val="272482367"/>
+        <c:axId val="1241985776"/>
+        <c:axId val="1241985296"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="272478047"/>
+        <c:axId val="1241985776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>year</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> and month </a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.4220688777539171"/>
+              <c:y val="0.88081811582062886"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1596,9 +1985,8 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+              <a:schemeClr val="bg1">
+                <a:alpha val="7000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -1612,9 +2000,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1625,7 +2012,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="272482367"/>
+        <c:crossAx val="1241985296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1633,7 +2020,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="272482367"/>
+        <c:axId val="1241985296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1643,9 +2030,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1653,7 +2040,73 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Revenue</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> ($)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.5404119939553011E-2"/>
+              <c:y val="0.33049394091695983"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1671,9 +2124,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1684,7 +2136,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="272478047"/>
+        <c:crossAx val="1241985776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1696,37 +2148,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1739,17 +2160,28 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -1774,7 +2206,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -1828,10 +2259,13 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent6"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent4"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -2368,35 +2802,33 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2404,26 +2836,34 @@
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:chartArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
     </cs:spPr>
     <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
@@ -2432,9 +2872,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2453,14 +2892,6 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -2469,20 +2900,20 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -2491,13 +2922,13 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -2509,10 +2940,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -2521,16 +2952,17 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -2548,21 +2980,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2572,20 +3001,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -2599,14 +3028,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -2620,9 +3049,8 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2636,12 +3064,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -2653,9 +3075,9 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2670,14 +3092,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -2689,14 +3110,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -2708,14 +3129,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -2724,14 +3144,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -2739,7 +3158,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -2752,11 +3171,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -2764,14 +3193,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2783,12 +3212,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -2804,7 +3240,6 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -2813,9 +3248,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2825,7 +3259,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -2833,9 +3267,9 @@
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -2846,9 +3280,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2860,12 +3293,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -2915,23 +3342,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>297180</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>502920</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3087DBBB-FF16-F8A7-FEBE-49957F14BBEC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F57705A-ABC3-E04D-BCE6-1FBAAFF489A3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3240,7 +3667,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1B77F3D1-CAB2-42CB-9BE9-FB1E173C2AC4}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1B77F3D1-CAB2-42CB-9BE9-FB1E173C2AC4}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A1:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField showAll="0">
@@ -3345,7 +3772,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{074E92FF-8C03-4C07-82EF-872838CD7271}" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{074E92FF-8C03-4C07-82EF-872838CD7271}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
   <location ref="A1:B54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -3547,12 +3974,51 @@
   <dataFields count="1">
     <dataField name="Sum of Monthly_Revenue" fld="2" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
+  <chartFormats count="4">
+    <chartFormat chart="18" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="9"/>
           </reference>
         </references>
       </pivotArea>
@@ -3906,7 +4372,7 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>433867.58</v>
       </c>
     </row>
@@ -3914,7 +4380,7 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>382843.07</v>
       </c>
     </row>
@@ -3922,7 +4388,7 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>399623.58</v>
       </c>
     </row>
@@ -3930,7 +4396,7 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>403062.69999999995</v>
       </c>
     </row>
@@ -3938,7 +4404,7 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>389390.88</v>
       </c>
     </row>
@@ -3946,7 +4412,7 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>397143.94000000006</v>
       </c>
     </row>
@@ -3954,7 +4420,7 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>427220.44999999995</v>
       </c>
     </row>
@@ -3962,7 +4428,7 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>431503.20999999996</v>
       </c>
     </row>
@@ -3970,7 +4436,7 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>442925.94000000006</v>
       </c>
     </row>
@@ -3978,7 +4444,7 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <v>553389.99</v>
       </c>
     </row>
@@ -3986,7 +4452,7 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12">
         <v>432040.42999999993</v>
       </c>
     </row>
@@ -3994,7 +4460,7 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13">
         <v>482394.10000000003</v>
       </c>
     </row>
@@ -4002,7 +4468,7 @@
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14">
         <v>5175405.8699999992</v>
       </c>
     </row>
@@ -4028,13 +4494,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4574,7 +5040,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E506FA8-DBF7-47C5-8485-632B51586BED}">
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:BB56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -4593,103 +5059,103 @@
       <c r="A2" s="2">
         <v>2022</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>879446.84000000008</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>70597.509999999995</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>63225.69</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>64779.71</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>78465.399999999994</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>73037.02</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>66868.55</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>72096.47</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>8</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>73904.91</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>9</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <v>77869.16</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>10</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12">
         <v>83610.78</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13">
         <v>70526.89</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>12</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14">
         <v>84464.75</v>
       </c>
     </row>
@@ -4697,323 +5163,474 @@
       <c r="A15" s="2">
         <v>2023</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15">
         <v>1212663.45</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>1</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16">
         <v>115439.64</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
         <v>2</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17">
         <v>91815.52</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
         <v>3</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18">
         <v>101529.42</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
         <v>4</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19">
         <v>94095.22</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
         <v>5</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20">
         <v>93011.83</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
         <v>6</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21">
         <v>88203.9</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
         <v>7</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22">
         <v>98822.98</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
         <v>8</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23">
         <v>107203.9</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
         <v>9</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24">
         <v>95680.79</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
         <v>10</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25">
         <v>108715.83</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
         <v>11</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26">
         <v>106648.71</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
         <v>12</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27">
         <v>111495.71</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>2024</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28">
         <v>1215290.46</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
         <v>1</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29">
         <v>99272.17</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
         <v>2</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30">
         <v>96699.78</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
         <v>3</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31">
         <v>95231.21</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="4">
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
         <v>4</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32">
         <v>91875.839999999997</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
         <v>5</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33">
         <v>89476.87</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
         <v>6</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34">
         <v>97550.01</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
         <v>7</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35">
         <v>107203.9</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
         <v>8</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36">
         <v>98470.41</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
+    <row r="37" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
         <v>9</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37">
         <v>105926.21</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
         <v>10</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38">
         <v>110232.92</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
         <v>11</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39">
         <v>107911.5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
         <v>12</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40">
         <v>115439.64</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>2025</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41">
         <v>1868005.1199999999</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
         <v>1</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42">
         <v>148558.26</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
         <v>2</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43">
         <v>131102.07999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
         <v>3</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44">
         <v>138083.24</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
         <v>4</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45">
         <v>138626.23999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
         <v>5</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46">
         <v>133865.16</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
         <v>6</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47">
         <v>144521.48000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
         <v>7</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48">
         <v>149097.1</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="4">
+    <row r="49" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
         <v>8</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49">
         <v>151923.99</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="4">
+    <row r="50" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
         <v>9</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50">
         <v>163449.78</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="4">
+    <row r="51" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
         <v>10</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51">
         <v>250830.46</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="4">
+    <row r="52" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
         <v>11</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52">
         <v>146953.32999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="4">
+    <row r="53" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
         <v>12</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53">
         <v>170994</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54">
         <v>5175405.870000001</v>
       </c>
     </row>
+    <row r="56" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="B56" s="2"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="2"/>
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="2"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
+      <c r="AR56" s="3"/>
+      <c r="AS56" s="3"/>
+      <c r="AT56" s="3"/>
+      <c r="AU56" s="3"/>
+      <c r="AV56" s="3"/>
+      <c r="AW56" s="3"/>
+      <c r="AX56" s="3"/>
+      <c r="AY56" s="3"/>
+      <c r="AZ56" s="3"/>
+      <c r="BA56" s="3"/>
+      <c r="BB56" s="2"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E27:Q33"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/Campusano_territory_chart.xlsx
+++ b/Campusano_territory_chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yanuriscampusano\Music\data_labs3\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CD8D6F-61FC-4FA3-8A9C-CCCF751A6F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA40AE88-60A5-4461-AF0D-B749E58D729B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" firstSheet="1" activeTab="2" xr2:uid="{3A3ABD6E-29B3-44B9-BCDA-4D764EC285EF}"/>
+    <workbookView xWindow="5148" yWindow="408" windowWidth="17460" windowHeight="13584" firstSheet="1" activeTab="2" xr2:uid="{3A3ABD6E-29B3-44B9-BCDA-4D764EC285EF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
   <si>
     <t>Year</t>
   </si>
@@ -45,7 +45,10 @@
     <t>Sum of Monthly_Revenue</t>
   </si>
   <si>
-    <t>This chart shows New Jersey territory monthly revenue from 2022 to 2025. You can see a clear upward trend. Revenue started around $63,000 to $84,000 per month in 2022 and grew consistently to over $140,000 per month by late 2024. The territory doubled its monthly revenue over this period which shows strong overall growth. The notable spike in October 2025 hitting $250,830 is unusual but it could be a large bulk purchase or a very successful marketing campaign that they should repeat it.</t>
+    <t>What is the month by month revenue breakdown for the New Jersey sales territory?</t>
+  </si>
+  <si>
+    <t>This chart shows New Jersey monthly revenue from 2022 to 2025. Revenue grew every year with each year performing better than the last. The spike in October 2025 of $250,830 stood out above all the other months and could be the result of a successful promotion that Miami Vue should repeat."</t>
   </si>
 </sst>
 </file>
@@ -551,7 +554,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -564,6 +567,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -5255,121 +5259,95 @@
         <v>106648.71</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>12</v>
       </c>
       <c r="B27">
         <v>111495.71</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6"/>
+    </row>
+    <row r="28" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>2024</v>
       </c>
       <c r="B28">
         <v>1215290.46</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
+    </row>
+    <row r="29" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>1</v>
       </c>
       <c r="B29">
         <v>99272.17</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+    </row>
+    <row r="30" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>2</v>
       </c>
       <c r="B30">
         <v>96699.78</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E30" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+    </row>
+    <row r="31" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>3</v>
       </c>
       <c r="B31">
         <v>95231.21</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+    </row>
+    <row r="32" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>4</v>
       </c>
       <c r="B32">
         <v>91875.839999999997</v>
       </c>
-      <c r="E32" s="5"/>
+      <c r="E32" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -5380,10 +5358,10 @@
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+    </row>
+    <row r="33" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>5</v>
       </c>
@@ -5401,104 +5379,218 @@
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+    </row>
+    <row r="34" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>6</v>
       </c>
       <c r="B34">
         <v>97550.01</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="6"/>
+    </row>
+    <row r="35" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>7</v>
       </c>
       <c r="B35">
         <v>107203.9</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="6"/>
+    </row>
+    <row r="36" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>8</v>
       </c>
       <c r="B36">
         <v>98470.41</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="6"/>
+    </row>
+    <row r="37" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>9</v>
       </c>
       <c r="B37">
         <v>105926.21</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="6"/>
+    </row>
+    <row r="38" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>10</v>
       </c>
       <c r="B38">
         <v>110232.92</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P38" s="6"/>
+    </row>
+    <row r="39" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>11</v>
       </c>
       <c r="B39">
         <v>107911.5</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P39" s="6"/>
+    </row>
+    <row r="40" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>12</v>
       </c>
       <c r="B40">
         <v>115439.64</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
+    </row>
+    <row r="41" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>2025</v>
       </c>
       <c r="B41">
         <v>1868005.1199999999</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+    </row>
+    <row r="42" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>1</v>
       </c>
       <c r="B42">
         <v>148558.26</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+    </row>
+    <row r="43" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>2</v>
       </c>
       <c r="B43">
         <v>131102.07999999999</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+    </row>
+    <row r="44" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>3</v>
       </c>
       <c r="B44">
         <v>138083.24</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+    </row>
+    <row r="45" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>4</v>
       </c>
       <c r="B45">
         <v>138626.23999999999</v>
       </c>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
@@ -5629,7 +5721,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E27:Q33"/>
+    <mergeCell ref="E32:O37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>

--- a/Campusano_territory_chart.xlsx
+++ b/Campusano_territory_chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yanuriscampusano\Music\data_labs3\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA40AE88-60A5-4461-AF0D-B749E58D729B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555B8C89-DF7C-4B19-B372-EE41E12B9865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5148" yWindow="408" windowWidth="17460" windowHeight="13584" firstSheet="1" activeTab="2" xr2:uid="{3A3ABD6E-29B3-44B9-BCDA-4D764EC285EF}"/>
   </bookViews>
@@ -554,7 +554,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -564,6 +564,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -5266,11 +5267,11 @@
       <c r="B27">
         <v>111495.71</v>
       </c>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
     </row>
     <row r="28" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
@@ -5279,9 +5280,9 @@
       <c r="B28">
         <v>1215290.46</v>
       </c>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
     </row>
     <row r="29" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
@@ -5290,9 +5291,9 @@
       <c r="B29">
         <v>99272.17</v>
       </c>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
     </row>
     <row r="30" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
@@ -5301,21 +5302,21 @@
       <c r="B30">
         <v>96699.78</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
     </row>
     <row r="31" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
@@ -5324,19 +5325,19 @@
       <c r="B31">
         <v>95231.21</v>
       </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
     </row>
     <row r="32" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
@@ -5345,21 +5346,21 @@
       <c r="B32">
         <v>91875.839999999997</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
     </row>
     <row r="33" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
@@ -5368,19 +5369,19 @@
       <c r="B33">
         <v>89476.87</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
     </row>
     <row r="34" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
@@ -5389,18 +5390,18 @@
       <c r="B34">
         <v>97550.01</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="5"/>
     </row>
     <row r="35" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
@@ -5409,18 +5410,18 @@
       <c r="B35">
         <v>107203.9</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="5"/>
     </row>
     <row r="36" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
@@ -5429,18 +5430,18 @@
       <c r="B36">
         <v>98470.41</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="7"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="5"/>
     </row>
     <row r="37" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
@@ -5449,18 +5450,18 @@
       <c r="B37">
         <v>105926.21</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
-      <c r="P37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="5"/>
     </row>
     <row r="38" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
@@ -5469,7 +5470,7 @@
       <c r="B38">
         <v>110232.92</v>
       </c>
-      <c r="P38" s="6"/>
+      <c r="P38" s="5"/>
     </row>
     <row r="39" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
@@ -5478,7 +5479,7 @@
       <c r="B39">
         <v>107911.5</v>
       </c>
-      <c r="P39" s="6"/>
+      <c r="P39" s="5"/>
     </row>
     <row r="40" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
@@ -5487,18 +5488,18 @@
       <c r="B40">
         <v>115439.64</v>
       </c>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="6"/>
-      <c r="N40" s="6"/>
-      <c r="O40" s="6"/>
-      <c r="P40" s="6"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
     </row>
     <row r="41" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
@@ -5507,18 +5508,18 @@
       <c r="B41">
         <v>1868005.1199999999</v>
       </c>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="6"/>
-      <c r="P41" s="6"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
     </row>
     <row r="42" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
@@ -5527,16 +5528,16 @@
       <c r="B42">
         <v>148558.26</v>
       </c>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="6"/>
-      <c r="N42" s="6"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
     </row>
     <row r="43" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
@@ -5545,16 +5546,16 @@
       <c r="B43">
         <v>131102.07999999999</v>
       </c>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="6"/>
-      <c r="N43" s="6"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
     </row>
     <row r="44" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
@@ -5563,16 +5564,16 @@
       <c r="B44">
         <v>138083.24</v>
       </c>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="6"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
     </row>
     <row r="45" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
@@ -5581,16 +5582,16 @@
       <c r="B45">
         <v>138626.23999999999</v>
       </c>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
@@ -5721,7 +5722,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E32:O37"/>
+    <mergeCell ref="E32:M37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
